--- a/excel/EnumData.xlsx
+++ b/excel/EnumData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11102"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/geugkkom/Documents/Tsomsomm/lunaria-data/excel/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hansu/lunaria-data/excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2CD6A90-5773-2145-914B-233BF4A18D7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42A530D0-AF0A-F647-823F-EB20D139FEAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7480" yWindow="680" windowWidth="13440" windowHeight="16520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4860" yWindow="1300" windowWidth="13440" windowHeight="16520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Enum" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="80">
   <si>
     <t>EnumName</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -503,6 +503,99 @@
   </si>
   <si>
     <t>펜던트</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>ArtifactRateUp</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>마도구</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>합성</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>성공</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>확률</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>증가</t>
+    </r>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -877,7 +970,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:E52"/>
+  <dimension ref="A1:E53"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.5" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="2" width="22.6640625" style="4" customWidth="1"/>
@@ -1232,16 +1325,16 @@
     </row>
     <row r="29" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="8" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="B29" s="4">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="D29" s="12" t="s">
-        <v>73</v>
+        <v>78</v>
+      </c>
+      <c r="D29" s="11" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="30" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -1249,13 +1342,13 @@
         <v>22</v>
       </c>
       <c r="B30" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D30" s="12" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="31" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -1263,13 +1356,13 @@
         <v>22</v>
       </c>
       <c r="B31" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D31" s="12" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -1277,13 +1370,13 @@
         <v>22</v>
       </c>
       <c r="B32" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D32" s="12" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="33" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -1291,24 +1384,27 @@
         <v>22</v>
       </c>
       <c r="B33" s="4">
+        <v>4</v>
+      </c>
+      <c r="C33" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D33" s="12" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="B34" s="4">
         <v>5</v>
       </c>
-      <c r="C33" s="7" t="s">
+      <c r="C34" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="D33" s="12" t="s">
+      <c r="D34" s="12" t="s">
         <v>77</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A34" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="B34" s="4">
-        <v>1</v>
-      </c>
-      <c r="C34" s="7" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="35" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -1316,10 +1412,10 @@
         <v>30</v>
       </c>
       <c r="B35" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="36" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -1327,21 +1423,21 @@
         <v>30</v>
       </c>
       <c r="B36" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="37" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="8" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B37" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="38" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -1349,10 +1445,10 @@
         <v>34</v>
       </c>
       <c r="B38" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
     </row>
     <row r="39" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -1360,10 +1456,10 @@
         <v>34</v>
       </c>
       <c r="B39" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="40" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -1371,21 +1467,21 @@
         <v>34</v>
       </c>
       <c r="B40" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C40" s="7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="41" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A41" s="8" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B41" s="4">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C41" s="7" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
     </row>
     <row r="42" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -1393,10 +1489,10 @@
         <v>38</v>
       </c>
       <c r="B42" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C42" s="7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="43" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -1404,10 +1500,10 @@
         <v>38</v>
       </c>
       <c r="B43" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C43" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="44" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -1415,32 +1511,32 @@
         <v>38</v>
       </c>
       <c r="B44" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C44" s="7" t="s">
-        <v>69</v>
+        <v>41</v>
       </c>
     </row>
     <row r="45" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A45" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="B45" s="4">
+        <v>4</v>
+      </c>
+      <c r="C45" s="7" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A46" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="B45" s="8">
+      <c r="B46" s="8">
         <v>1</v>
       </c>
-      <c r="C45" s="8" t="s">
+      <c r="C46" s="8" t="s">
         <v>44</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A46" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="B46" s="8">
-        <v>2</v>
-      </c>
-      <c r="C46" s="8" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="47" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -1448,21 +1544,21 @@
         <v>42</v>
       </c>
       <c r="B47" s="8">
+        <v>2</v>
+      </c>
+      <c r="C47" s="8" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A48" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B48" s="8">
         <v>3</v>
       </c>
-      <c r="C47" s="8" t="s">
+      <c r="C48" s="8" t="s">
         <v>46</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A48" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="B48" s="4">
-        <v>1</v>
-      </c>
-      <c r="C48" s="8" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="49" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -1470,10 +1566,10 @@
         <v>47</v>
       </c>
       <c r="B49" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C49" s="8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="50" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -1481,17 +1577,28 @@
         <v>47</v>
       </c>
       <c r="B50" s="4">
+        <v>2</v>
+      </c>
+      <c r="C50" s="8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A51" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="B51" s="4">
         <v>3</v>
       </c>
-      <c r="C50" s="8" t="s">
+      <c r="C51" s="8" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="51" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A51" s="10"/>
     </row>
     <row r="52" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A52" s="10"/>
+    </row>
+    <row r="53" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A53" s="10"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
